--- a/src/app/modules/dashboard/excel_files/spice-it-up-100-hot-spicy-whole-food-plant-based-recipes-autosaved.xlsx
+++ b/src/app/modules/dashboard/excel_files/spice-it-up-100-hot-spicy-whole-food-plant-based-recipes-autosaved.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4065,7 +4065,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -4247,7 +4247,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4948,7 +4948,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5047,7 +5047,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6032,7 +6032,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6613,7 +6613,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6623,7 +6623,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6713,7 +6713,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6723,7 +6723,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6914,7 +6914,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -7013,7 +7013,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -7222,7 +7222,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -7411,7 +7411,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7510,7 +7510,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -7619,7 +7619,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7708,7 +7708,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -7915,7 +7915,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -8004,7 +8004,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -8014,7 +8014,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -8202,7 +8202,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -8311,7 +8311,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -8401,7 +8401,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -8512,7 +8512,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -8603,7 +8603,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -8703,7 +8703,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -8713,7 +8713,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -8803,7 +8803,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -8813,7 +8813,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -8902,7 +8902,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -8912,7 +8912,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -9096,7 +9096,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -9195,7 +9195,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -9205,7 +9205,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -9295,7 +9295,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'breakfast', 'lunches-and-dinners', 'soups', 'salads', 'stir-fry', 'wraps', 'bowls', 'desserts']</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -9305,7 +9305,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
